--- a/Grupos CE.xlsx
+++ b/Grupos CE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sazofeifa/Documents/Tec/2026/semestre2/Paradigmas/Proyecto_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577225F7-9075-D948-B250-C6F0972A3DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF75E5D-9F78-9A49-8894-65DF0EB932C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4420" yWindow="660" windowWidth="24980" windowHeight="17340" xr2:uid="{D7D856E2-35E9-9F46-A1F8-C4B1BC39664A}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="24980" windowHeight="17340" activeTab="1" xr2:uid="{D7D856E2-35E9-9F46-A1F8-C4B1BC39664A}"/>
   </bookViews>
   <sheets>
     <sheet name="Todo" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="304">
   <si>
     <t>Código</t>
   </si>
@@ -817,13 +817,145 @@
   </si>
   <si>
     <t>Villalta Romero Fabian</t>
+  </si>
+  <si>
+    <t>EM5001</t>
+  </si>
+  <si>
+    <t>Historia de las matemáticas</t>
+  </si>
+  <si>
+    <t>Meza Cascante Luis Gerardo</t>
+  </si>
+  <si>
+    <t>EM5002</t>
+  </si>
+  <si>
+    <t>Didáctica de las matemáticas I</t>
+  </si>
+  <si>
+    <t>Agüero Calvo Evelyn</t>
+  </si>
+  <si>
+    <t>Jue 17:00–19:50</t>
+  </si>
+  <si>
+    <t>EM5003</t>
+  </si>
+  <si>
+    <t>Taller I: algoritmos y programación</t>
+  </si>
+  <si>
+    <t>Marrero Calvo Marcela</t>
+  </si>
+  <si>
+    <t>EM5004</t>
+  </si>
+  <si>
+    <t>Introducción al análisis funcional</t>
+  </si>
+  <si>
+    <t>Masís Flores David</t>
+  </si>
+  <si>
+    <t>Vie 17:00–20:50</t>
+  </si>
+  <si>
+    <t>EM5005</t>
+  </si>
+  <si>
+    <t>Teoría de números</t>
+  </si>
+  <si>
+    <t>Sanabria Brenes Geovanni</t>
+  </si>
+  <si>
+    <t>Jue 17:00–20:50</t>
+  </si>
+  <si>
+    <t>EM5006</t>
+  </si>
+  <si>
+    <t>Didáctica de las matemáticas II</t>
+  </si>
+  <si>
+    <t>Acuña Chacón Reiman</t>
+  </si>
+  <si>
+    <t>Vie 17:00–19:50</t>
+  </si>
+  <si>
+    <t>EM5007</t>
+  </si>
+  <si>
+    <t>Taller II: multimedios en matemática</t>
+  </si>
+  <si>
+    <t>Monge Fallas Jorge</t>
+  </si>
+  <si>
+    <t>EM5008</t>
+  </si>
+  <si>
+    <t>Investigación educativa</t>
+  </si>
+  <si>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>Requisitos / Correquisitos</t>
+  </si>
+  <si>
+    <t>Req: — / Correq: —</t>
+  </si>
+  <si>
+    <t>Req: CE1101, CE1104, MA1403 / Correq: —</t>
+  </si>
+  <si>
+    <t>Req: — / Correq: CE1101</t>
+  </si>
+  <si>
+    <t>Req: CE1104 / Correq: —</t>
+  </si>
+  <si>
+    <t>Req: CE1103, CE1105 / Correq: —</t>
+  </si>
+  <si>
+    <t>Req: MA0101 / Correq: —</t>
+  </si>
+  <si>
+    <t>Req: MA1102 / Correq: —</t>
+  </si>
+  <si>
+    <t>Req: MA1103 / Correq: —</t>
+  </si>
+  <si>
+    <t>Req: — / Correq: FI1101</t>
+  </si>
+  <si>
+    <t>Req: FI1201 / Correq: FI1102</t>
+  </si>
+  <si>
+    <t>Req: — / Correq: QU1106</t>
+  </si>
+  <si>
+    <t>Req: — / Correq: QU1102</t>
+  </si>
+  <si>
+    <t>Req: FI1101, MA1102 / Correq: —</t>
+  </si>
+  <si>
+    <t>Req: FI1101 / Correq: MA1102</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -837,6 +969,13 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -860,7 +999,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -870,6 +1009,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4718,13 +4860,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34AB29DF-02E3-1A42-97EB-376FB1E7305B}">
-  <dimension ref="D3:L118"/>
+  <dimension ref="D1:X118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="4"/>
+    <col min="1" max="12" width="10.83203125" style="4"/>
+    <col min="13" max="13" width="18.5" style="4" customWidth="1"/>
+    <col min="14" max="23" width="10.83203125" style="4"/>
+    <col min="24" max="24" width="18.33203125" style="4" customWidth="1"/>
+    <col min="25" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="4:24" ht="17" x14ac:dyDescent="0.2">
+      <c r="D1" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="3" spans="4:24" ht="68" x14ac:dyDescent="0.2">
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
@@ -4752,8 +4906,41 @@
       <c r="L3" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M3" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4" spans="4:24" ht="68" x14ac:dyDescent="0.2">
       <c r="D4" s="4" t="s">
         <v>6</v>
       </c>
@@ -4781,8 +4968,41 @@
       <c r="L4" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="5" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M4" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="O4" t="s">
+        <v>260</v>
+      </c>
+      <c r="P4" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4" t="s">
+        <v>144</v>
+      </c>
+      <c r="S4" t="s">
+        <v>262</v>
+      </c>
+      <c r="T4" t="s">
+        <v>146</v>
+      </c>
+      <c r="U4">
+        <v>4</v>
+      </c>
+      <c r="V4">
+        <v>3</v>
+      </c>
+      <c r="W4" t="s">
+        <v>67</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="4:24" ht="68" x14ac:dyDescent="0.2">
       <c r="D5" s="4" t="s">
         <v>6</v>
       </c>
@@ -4810,8 +5030,41 @@
       <c r="L5" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="6" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M5" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="O5" t="s">
+        <v>263</v>
+      </c>
+      <c r="P5" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5" t="s">
+        <v>144</v>
+      </c>
+      <c r="S5" t="s">
+        <v>265</v>
+      </c>
+      <c r="T5" t="s">
+        <v>266</v>
+      </c>
+      <c r="U5">
+        <v>4</v>
+      </c>
+      <c r="V5">
+        <v>3</v>
+      </c>
+      <c r="W5" t="s">
+        <v>67</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="4:24" ht="68" x14ac:dyDescent="0.2">
       <c r="D6" s="4" t="s">
         <v>6</v>
       </c>
@@ -4839,8 +5092,41 @@
       <c r="L6" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="7" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M6" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="O6" t="s">
+        <v>267</v>
+      </c>
+      <c r="P6" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6" t="s">
+        <v>144</v>
+      </c>
+      <c r="S6" t="s">
+        <v>269</v>
+      </c>
+      <c r="T6" t="s">
+        <v>222</v>
+      </c>
+      <c r="U6">
+        <v>4</v>
+      </c>
+      <c r="V6">
+        <v>3</v>
+      </c>
+      <c r="W6" t="s">
+        <v>67</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="4:24" ht="68" x14ac:dyDescent="0.2">
       <c r="D7" s="4" t="s">
         <v>6</v>
       </c>
@@ -4868,8 +5154,41 @@
       <c r="L7" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="8" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M7" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="O7" t="s">
+        <v>270</v>
+      </c>
+      <c r="P7" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>144</v>
+      </c>
+      <c r="S7" t="s">
+        <v>272</v>
+      </c>
+      <c r="T7" t="s">
+        <v>273</v>
+      </c>
+      <c r="U7">
+        <v>4</v>
+      </c>
+      <c r="V7">
+        <v>4</v>
+      </c>
+      <c r="W7" t="s">
+        <v>67</v>
+      </c>
+      <c r="X7" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="8" spans="4:24" ht="68" x14ac:dyDescent="0.2">
       <c r="D8" s="4" t="s">
         <v>6</v>
       </c>
@@ -4897,8 +5216,41 @@
       <c r="L8" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M8" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="O8" t="s">
+        <v>274</v>
+      </c>
+      <c r="P8" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S8" t="s">
+        <v>276</v>
+      </c>
+      <c r="T8" t="s">
+        <v>277</v>
+      </c>
+      <c r="U8">
+        <v>4</v>
+      </c>
+      <c r="V8">
+        <v>4</v>
+      </c>
+      <c r="W8" t="s">
+        <v>67</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="4:24" ht="68" x14ac:dyDescent="0.2">
       <c r="D9" s="4" t="s">
         <v>10</v>
       </c>
@@ -4926,8 +5278,41 @@
       <c r="L9" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M9" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="O9" t="s">
+        <v>278</v>
+      </c>
+      <c r="P9" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9" t="s">
+        <v>144</v>
+      </c>
+      <c r="S9" t="s">
+        <v>280</v>
+      </c>
+      <c r="T9" t="s">
+        <v>281</v>
+      </c>
+      <c r="U9">
+        <v>4</v>
+      </c>
+      <c r="V9">
+        <v>3</v>
+      </c>
+      <c r="W9" t="s">
+        <v>67</v>
+      </c>
+      <c r="X9" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="4:24" ht="68" x14ac:dyDescent="0.2">
       <c r="D10" s="4" t="s">
         <v>10</v>
       </c>
@@ -4955,8 +5340,41 @@
       <c r="L10" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="11" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M10" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="O10" t="s">
+        <v>282</v>
+      </c>
+      <c r="P10" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10" t="s">
+        <v>144</v>
+      </c>
+      <c r="S10" t="s">
+        <v>284</v>
+      </c>
+      <c r="T10" t="s">
+        <v>222</v>
+      </c>
+      <c r="U10">
+        <v>4</v>
+      </c>
+      <c r="V10">
+        <v>3</v>
+      </c>
+      <c r="W10" t="s">
+        <v>67</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="4:24" ht="68" x14ac:dyDescent="0.2">
       <c r="D11" s="4" t="s">
         <v>10</v>
       </c>
@@ -4984,8 +5402,41 @@
       <c r="L11" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="12" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M11" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="O11" t="s">
+        <v>285</v>
+      </c>
+      <c r="P11" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>144</v>
+      </c>
+      <c r="S11" t="s">
+        <v>262</v>
+      </c>
+      <c r="T11" t="s">
+        <v>146</v>
+      </c>
+      <c r="U11">
+        <v>4</v>
+      </c>
+      <c r="V11">
+        <v>3</v>
+      </c>
+      <c r="W11" t="s">
+        <v>67</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="4:24" ht="68" x14ac:dyDescent="0.2">
       <c r="D12" s="4" t="s">
         <v>10</v>
       </c>
@@ -5013,8 +5464,11 @@
       <c r="L12" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M12" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="13" spans="4:24" ht="85" x14ac:dyDescent="0.2">
       <c r="D13" s="4" t="s">
         <v>8</v>
       </c>
@@ -5042,8 +5496,11 @@
       <c r="L13" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M13" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="14" spans="4:24" ht="85" x14ac:dyDescent="0.2">
       <c r="D14" s="4" t="s">
         <v>8</v>
       </c>
@@ -5071,8 +5528,11 @@
       <c r="L14" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="15" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M14" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="15" spans="4:24" ht="85" x14ac:dyDescent="0.2">
       <c r="D15" s="4" t="s">
         <v>8</v>
       </c>
@@ -5100,8 +5560,11 @@
       <c r="L15" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="16" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M15" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="16" spans="4:24" ht="85" x14ac:dyDescent="0.2">
       <c r="D16" s="4" t="s">
         <v>8</v>
       </c>
@@ -5129,8 +5592,11 @@
       <c r="L16" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="17" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M16" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="17" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D17" s="4" t="s">
         <v>8</v>
       </c>
@@ -5158,8 +5624,11 @@
       <c r="L17" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="18" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M17" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="18" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D18" s="4" t="s">
         <v>8</v>
       </c>
@@ -5187,8 +5656,11 @@
       <c r="L18" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="19" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M18" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="19" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D19" s="4" t="s">
         <v>13</v>
       </c>
@@ -5216,8 +5688,11 @@
       <c r="L19" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="20" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M19" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D20" s="4" t="s">
         <v>13</v>
       </c>
@@ -5245,8 +5720,11 @@
       <c r="L20" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="21" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M20" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="21" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D21" s="4" t="s">
         <v>13</v>
       </c>
@@ -5274,8 +5752,11 @@
       <c r="L21" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="22" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M21" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="22" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D22" s="4" t="s">
         <v>13</v>
       </c>
@@ -5303,8 +5784,11 @@
       <c r="L22" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="23" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M22" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="23" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D23" s="4" t="s">
         <v>18</v>
       </c>
@@ -5332,8 +5816,11 @@
       <c r="L23" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="24" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M23" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="24" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D24" s="4" t="s">
         <v>18</v>
       </c>
@@ -5361,8 +5848,11 @@
       <c r="L24" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="25" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M24" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="25" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D25" s="4" t="s">
         <v>18</v>
       </c>
@@ -5390,8 +5880,11 @@
       <c r="L25" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="26" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M25" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="26" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D26" s="4" t="s">
         <v>18</v>
       </c>
@@ -5419,8 +5912,11 @@
       <c r="L26" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="27" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M26" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="27" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D27" s="4" t="s">
         <v>15</v>
       </c>
@@ -5448,8 +5944,11 @@
       <c r="L27" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="28" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M27" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D28" s="4" t="s">
         <v>15</v>
       </c>
@@ -5477,8 +5976,11 @@
       <c r="L28" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="29" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M28" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="29" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D29" s="4" t="s">
         <v>15</v>
       </c>
@@ -5506,8 +6008,11 @@
       <c r="L29" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="30" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M29" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="30" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D30" s="3" t="s">
         <v>63</v>
       </c>
@@ -5535,8 +6040,11 @@
       <c r="L30" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="31" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M30" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="31" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D31" s="3" t="s">
         <v>63</v>
       </c>
@@ -5564,8 +6072,11 @@
       <c r="L31" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="32" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M31" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D32" s="3" t="s">
         <v>63</v>
       </c>
@@ -5593,8 +6104,11 @@
       <c r="L32" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="33" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M32" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="33" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D33" s="3" t="s">
         <v>63</v>
       </c>
@@ -5622,8 +6136,11 @@
       <c r="L33" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="34" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M33" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="34" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D34" s="3" t="s">
         <v>63</v>
       </c>
@@ -5651,8 +6168,11 @@
       <c r="L34" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="35" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M34" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="35" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D35" s="3" t="s">
         <v>77</v>
       </c>
@@ -5680,8 +6200,11 @@
       <c r="L35" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="36" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M35" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="36" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D36" s="3" t="s">
         <v>77</v>
       </c>
@@ -5709,8 +6232,11 @@
       <c r="L36" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="37" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M36" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="37" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D37" s="3" t="s">
         <v>77</v>
       </c>
@@ -5738,8 +6264,11 @@
       <c r="L37" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="38" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M37" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="38" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D38" s="3" t="s">
         <v>77</v>
       </c>
@@ -5767,8 +6296,11 @@
       <c r="L38" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="39" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M38" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="39" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D39" s="3" t="s">
         <v>77</v>
       </c>
@@ -5796,8 +6328,11 @@
       <c r="L39" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="40" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M39" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="40" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D40" s="3" t="s">
         <v>86</v>
       </c>
@@ -5825,8 +6360,11 @@
       <c r="L40" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="41" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M40" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="41" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D41" s="3" t="s">
         <v>86</v>
       </c>
@@ -5854,8 +6392,11 @@
       <c r="L41" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="42" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M41" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D42" s="3" t="s">
         <v>86</v>
       </c>
@@ -5883,8 +6424,11 @@
       <c r="L42" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="43" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M42" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="43" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D43" s="3" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6456,11 @@
       <c r="L43" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="44" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M43" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="44" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D44" s="3" t="s">
         <v>86</v>
       </c>
@@ -5941,8 +6488,11 @@
       <c r="L44" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="45" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M44" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="45" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D45" s="3" t="s">
         <v>94</v>
       </c>
@@ -5970,8 +6520,11 @@
       <c r="L45" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="46" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M45" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="46" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D46" s="3" t="s">
         <v>94</v>
       </c>
@@ -5999,8 +6552,11 @@
       <c r="L46" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="47" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M46" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="47" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D47" s="3" t="s">
         <v>94</v>
       </c>
@@ -6028,8 +6584,11 @@
       <c r="L47" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="48" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M47" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="48" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D48" s="3" t="s">
         <v>94</v>
       </c>
@@ -6057,8 +6616,11 @@
       <c r="L48" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="49" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M48" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="49" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D49" s="3" t="s">
         <v>94</v>
       </c>
@@ -6086,8 +6648,11 @@
       <c r="L49" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="50" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M49" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="50" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D50" s="3" t="s">
         <v>101</v>
       </c>
@@ -6115,8 +6680,11 @@
       <c r="L50" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="51" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M50" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D51" s="3" t="s">
         <v>101</v>
       </c>
@@ -6144,8 +6712,11 @@
       <c r="L51" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="52" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M51" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="52" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D52" s="3" t="s">
         <v>101</v>
       </c>
@@ -6173,8 +6744,11 @@
       <c r="L52" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="53" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M52" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="53" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D53" s="3" t="s">
         <v>101</v>
       </c>
@@ -6202,8 +6776,11 @@
       <c r="L53" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="54" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M53" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="54" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D54" s="3" t="s">
         <v>101</v>
       </c>
@@ -6231,8 +6808,11 @@
       <c r="L54" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="55" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M54" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="55" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D55" s="4" t="s">
         <v>109</v>
       </c>
@@ -6260,8 +6840,11 @@
       <c r="L55" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="56" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M55" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="56" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D56" s="4" t="s">
         <v>109</v>
       </c>
@@ -6289,8 +6872,11 @@
       <c r="L56" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="57" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M56" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="57" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D57" s="4" t="s">
         <v>109</v>
       </c>
@@ -6318,8 +6904,11 @@
       <c r="L57" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="58" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M57" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="58" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D58" s="4" t="s">
         <v>109</v>
       </c>
@@ -6347,8 +6936,11 @@
       <c r="L58" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="59" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M58" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="59" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D59" s="4" t="s">
         <v>113</v>
       </c>
@@ -6376,8 +6968,11 @@
       <c r="L59" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="60" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M59" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="60" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D60" s="4" t="s">
         <v>113</v>
       </c>
@@ -6405,8 +7000,11 @@
       <c r="L60" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="61" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M60" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="61" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D61" s="4" t="s">
         <v>113</v>
       </c>
@@ -6434,8 +7032,11 @@
       <c r="L61" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="62" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M61" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="62" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D62" s="4" t="s">
         <v>113</v>
       </c>
@@ -6463,8 +7064,11 @@
       <c r="L62" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="63" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M62" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="63" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D63" s="4" t="s">
         <v>113</v>
       </c>
@@ -6492,8 +7096,11 @@
       <c r="L63" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="64" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M63" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="64" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D64" s="4" t="s">
         <v>118</v>
       </c>
@@ -6521,8 +7128,11 @@
       <c r="L64" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="65" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M64" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="65" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D65" s="4" t="s">
         <v>118</v>
       </c>
@@ -6550,8 +7160,11 @@
       <c r="L65" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="66" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M65" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="66" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D66" s="4" t="s">
         <v>118</v>
       </c>
@@ -6579,8 +7192,11 @@
       <c r="L66" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="67" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M66" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="67" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D67" s="4" t="s">
         <v>118</v>
       </c>
@@ -6608,8 +7224,11 @@
       <c r="L67" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="68" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M67" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="68" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D68" s="4" t="s">
         <v>118</v>
       </c>
@@ -6637,8 +7256,11 @@
       <c r="L68" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M68" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="69" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D69" s="4" t="s">
         <v>128</v>
       </c>
@@ -6666,8 +7288,11 @@
       <c r="L69" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="70" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M69" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="70" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D70" s="4" t="s">
         <v>128</v>
       </c>
@@ -6695,8 +7320,11 @@
       <c r="L70" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="71" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M70" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="71" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D71" s="4" t="s">
         <v>128</v>
       </c>
@@ -6724,8 +7352,11 @@
       <c r="L71" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="72" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M71" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="72" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D72" s="4" t="s">
         <v>128</v>
       </c>
@@ -6753,8 +7384,11 @@
       <c r="L72" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="73" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M72" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="73" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D73" s="4" t="s">
         <v>128</v>
       </c>
@@ -6782,8 +7416,11 @@
       <c r="L73" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="74" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M73" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="74" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D74" s="4" t="s">
         <v>134</v>
       </c>
@@ -6811,8 +7448,11 @@
       <c r="L74" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="75" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M74" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="75" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D75" s="4" t="s">
         <v>134</v>
       </c>
@@ -6840,8 +7480,11 @@
       <c r="L75" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="76" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M75" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="76" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D76" s="4" t="s">
         <v>134</v>
       </c>
@@ -6869,8 +7512,11 @@
       <c r="L76" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="77" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M76" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="77" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D77" s="4" t="s">
         <v>134</v>
       </c>
@@ -6898,8 +7544,11 @@
       <c r="L77" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="78" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M77" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="78" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D78" s="4" t="s">
         <v>134</v>
       </c>
@@ -6927,8 +7576,11 @@
       <c r="L78" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="79" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M78" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="79" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D79" s="4" t="s">
         <v>256</v>
       </c>
@@ -6956,8 +7608,11 @@
       <c r="L79" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="80" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M79" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="80" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D80" s="4" t="s">
         <v>256</v>
       </c>
@@ -6985,8 +7640,11 @@
       <c r="L80" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="81" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M80" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="81" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D81" s="4" t="s">
         <v>256</v>
       </c>
@@ -7014,8 +7672,11 @@
       <c r="L81" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="82" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M81" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="82" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D82" s="4" t="s">
         <v>256</v>
       </c>
@@ -7043,8 +7704,11 @@
       <c r="L82" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="83" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M82" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="83" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D83" s="4" t="s">
         <v>256</v>
       </c>
@@ -7072,8 +7736,11 @@
       <c r="L83" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="84" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M83" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="84" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D84" s="4" t="s">
         <v>142</v>
       </c>
@@ -7101,8 +7768,11 @@
       <c r="L84" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="85" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M84" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="85" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D85" s="4" t="s">
         <v>142</v>
       </c>
@@ -7130,8 +7800,11 @@
       <c r="L85" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="86" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M85" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="86" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D86" s="4" t="s">
         <v>142</v>
       </c>
@@ -7159,8 +7832,11 @@
       <c r="L86" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="87" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M86" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="87" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D87" s="4" t="s">
         <v>142</v>
       </c>
@@ -7188,8 +7864,11 @@
       <c r="L87" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="88" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M87" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="88" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D88" s="4" t="s">
         <v>142</v>
       </c>
@@ -7217,8 +7896,11 @@
       <c r="L88" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="89" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M88" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="89" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D89" s="4" t="s">
         <v>151</v>
       </c>
@@ -7246,8 +7928,11 @@
       <c r="L89" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="90" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M89" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="90" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D90" s="4" t="s">
         <v>151</v>
       </c>
@@ -7275,8 +7960,11 @@
       <c r="L90" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="91" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M90" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="91" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D91" s="4" t="s">
         <v>151</v>
       </c>
@@ -7304,8 +7992,11 @@
       <c r="L91" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="92" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M91" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="92" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D92" s="4" t="s">
         <v>151</v>
       </c>
@@ -7333,8 +8024,11 @@
       <c r="L92" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="93" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M92" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="93" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D93" s="4" t="s">
         <v>151</v>
       </c>
@@ -7362,8 +8056,11 @@
       <c r="L93" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="94" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M93" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="94" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D94" s="4" t="s">
         <v>156</v>
       </c>
@@ -7391,8 +8088,11 @@
       <c r="L94" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="95" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M94" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="95" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D95" s="4" t="s">
         <v>156</v>
       </c>
@@ -7420,8 +8120,11 @@
       <c r="L95" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="96" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M95" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="96" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D96" s="4" t="s">
         <v>156</v>
       </c>
@@ -7449,8 +8152,11 @@
       <c r="L96" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="97" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M96" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="97" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D97" s="4" t="s">
         <v>156</v>
       </c>
@@ -7478,8 +8184,11 @@
       <c r="L97" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="98" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M97" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="98" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D98" s="4" t="s">
         <v>156</v>
       </c>
@@ -7507,8 +8216,11 @@
       <c r="L98" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="99" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M98" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="99" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D99" s="4" t="s">
         <v>167</v>
       </c>
@@ -7536,8 +8248,11 @@
       <c r="L99" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="100" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M99" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="100" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D100" s="4" t="s">
         <v>167</v>
       </c>
@@ -7565,8 +8280,11 @@
       <c r="L100" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="101" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M100" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="101" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D101" s="4" t="s">
         <v>167</v>
       </c>
@@ -7594,8 +8312,11 @@
       <c r="L101" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="102" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M101" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="102" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D102" s="4" t="s">
         <v>167</v>
       </c>
@@ -7623,8 +8344,11 @@
       <c r="L102" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="103" spans="4:12" ht="85" x14ac:dyDescent="0.2">
+      <c r="M102" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="103" spans="4:13" ht="85" x14ac:dyDescent="0.2">
       <c r="D103" s="4" t="s">
         <v>167</v>
       </c>
@@ -7652,8 +8376,11 @@
       <c r="L103" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="104" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M103" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="104" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D104" s="4" t="s">
         <v>175</v>
       </c>
@@ -7681,8 +8408,11 @@
       <c r="L104" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="105" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M104" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="105" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D105" s="4" t="s">
         <v>178</v>
       </c>
@@ -7710,8 +8440,11 @@
       <c r="L105" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="106" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M105" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="106" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D106" s="4" t="s">
         <v>182</v>
       </c>
@@ -7739,8 +8472,11 @@
       <c r="L106" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="107" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M106" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="107" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D107" s="4" t="s">
         <v>185</v>
       </c>
@@ -7768,8 +8504,11 @@
       <c r="L107" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="108" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M107" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="108" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D108" s="4" t="s">
         <v>189</v>
       </c>
@@ -7797,8 +8536,11 @@
       <c r="L108" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="109" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M108" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="109" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D109" s="4" t="s">
         <v>193</v>
       </c>
@@ -7826,8 +8568,11 @@
       <c r="L109" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="110" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M109" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="110" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D110" s="4" t="s">
         <v>196</v>
       </c>
@@ -7855,8 +8600,11 @@
       <c r="L110" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="111" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M110" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="111" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D111" s="4" t="s">
         <v>200</v>
       </c>
@@ -7884,8 +8632,11 @@
       <c r="L111" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="112" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M111" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="112" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D112" s="4" t="s">
         <v>203</v>
       </c>
@@ -7913,8 +8664,11 @@
       <c r="L112" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="113" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M112" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="113" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D113" s="4" t="s">
         <v>205</v>
       </c>
@@ -7942,8 +8696,11 @@
       <c r="L113" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="114" spans="4:12" ht="102" x14ac:dyDescent="0.2">
+      <c r="M113" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="114" spans="4:13" ht="102" x14ac:dyDescent="0.2">
       <c r="D114" s="4" t="s">
         <v>208</v>
       </c>
@@ -7971,8 +8728,11 @@
       <c r="L114" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="115" spans="4:12" ht="119" x14ac:dyDescent="0.2">
+      <c r="M114" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="115" spans="4:13" ht="119" x14ac:dyDescent="0.2">
       <c r="D115" s="4" t="s">
         <v>212</v>
       </c>
@@ -8000,8 +8760,11 @@
       <c r="L115" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="116" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M115" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="116" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D116" s="4" t="s">
         <v>216</v>
       </c>
@@ -8029,8 +8792,11 @@
       <c r="L116" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="117" spans="4:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="M116" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="117" spans="4:13" ht="51" x14ac:dyDescent="0.2">
       <c r="D117" s="4" t="s">
         <v>219</v>
       </c>
@@ -8058,8 +8824,11 @@
       <c r="L117" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="118" spans="4:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="M117" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="118" spans="4:13" ht="68" x14ac:dyDescent="0.2">
       <c r="D118" s="4" t="s">
         <v>223</v>
       </c>
@@ -8086,6 +8855,9 @@
       </c>
       <c r="L118" s="4" t="s">
         <v>67</v>
+      </c>
+      <c r="M118" s="4" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
